--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(1).xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="498">
   <si>
     <t>ID</t>
   </si>
@@ -447,6 +447,9 @@
     <t>43</t>
   </si>
   <si>
+    <t>你甚至能听到其中一名医生正在说话，她的声音平静得像是念一份实验报告：“……103号和101号适配度都超过80%，优先安排在二层的监护病房，等镇静剂代谢完毕就可以开始第一次意识连接测试。”</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=27</t>
   </si>
   <si>
@@ -753,7 +756,7 @@
     <t>那张温和的脸从眉心开始裂成两半，正如他一分为二的人格那样。一半朝着悬在左侧的光圈滑去，另外一半则随着机关的启动缓慢移向了右侧的阴影。露出中间一道仅容一人通过的、向下延伸的通道入口。</t>
   </si>
   <si>
-    <t>parallel(bgfade(sntzm_gy(1)_93,1);shake(screen,0.5,5);playsfx(GearSpinning))</t>
+    <t>parallel(bgfade(sntzm_gy(1)_93,1);shake(screen,1,2);playsfx(GearSpinning))</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=59</t>
@@ -811,6 +814,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -949,6 +957,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -1027,6 +1040,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>charfadeout(L,1)&amp;loadScript(</t>
     </r>
     <r>
@@ -3003,7 +3021,7 @@
         <v>15</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="G6" t="s">
         <v>35</v>
@@ -4202,7 +4220,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="38" spans="1:12">
+    <row r="38" ht="58.5" spans="1:12">
       <c r="A38" t="s">
         <v>136</v>
       </c>
@@ -4222,7 +4240,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>137</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4237,12 +4255,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="39" ht="28.5" spans="1:12">
       <c r="A39" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4260,7 +4278,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4275,12 +4293,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="40" ht="27" spans="1:12">
       <c r="A40" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4298,7 +4316,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4313,12 +4331,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="41" ht="54" spans="1:12">
       <c r="A41" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4336,7 +4354,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4351,12 +4369,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="42" ht="54" spans="1:12">
       <c r="A42" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4374,7 +4392,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4386,15 +4404,15 @@
         <v>15</v>
       </c>
       <c r="K42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="L42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4427,12 +4445,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="44" ht="30" spans="1:12">
       <c r="A44" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B44" t="s">
         <v>23</v>
@@ -4450,7 +4468,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4465,12 +4483,12 @@
         <v>26</v>
       </c>
       <c r="L44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="45" ht="30" spans="1:12">
       <c r="A45" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4488,7 +4506,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4500,15 +4518,15 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4526,7 +4544,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4541,12 +4559,12 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B47" t="s">
         <v>107</v>
@@ -4564,7 +4582,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4579,12 +4597,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" ht="30" spans="1:12">
       <c r="A48" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B48" t="s">
         <v>23</v>
@@ -4602,7 +4620,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4617,12 +4635,12 @@
         <v>26</v>
       </c>
       <c r="L48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="49" ht="30" spans="1:12">
       <c r="A49" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4640,7 +4658,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4655,12 +4673,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B50" t="s">
         <v>23</v>
@@ -4678,7 +4696,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4693,12 +4711,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4716,7 +4734,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4731,12 +4749,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="52" ht="30" spans="1:12">
       <c r="A52" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B52" t="s">
         <v>23</v>
@@ -4754,7 +4772,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4769,12 +4787,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="53" ht="42" spans="1:12">
       <c r="A53" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4792,7 +4810,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4804,15 +4822,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="54" ht="55.5" spans="1:12">
       <c r="A54" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4830,7 +4848,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4845,12 +4863,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4868,7 +4886,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4883,12 +4901,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="56" ht="40.5" spans="1:12">
       <c r="A56" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4906,7 +4924,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4921,12 +4939,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="57" ht="55.5" spans="1:12">
       <c r="A57" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4944,7 +4962,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4956,12 +4974,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="58" spans="1:12">
       <c r="A58" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4994,12 +5012,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="59" ht="90" spans="1:12">
       <c r="A59" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5017,7 +5035,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5029,15 +5047,15 @@
         <v>15</v>
       </c>
       <c r="K59" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L59" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="60" ht="90" spans="1:12">
       <c r="A60" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5055,7 +5073,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5070,12 +5088,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="61" ht="30" spans="1:12">
       <c r="A61" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B61" t="s">
         <v>23</v>
@@ -5093,7 +5111,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5108,12 +5126,12 @@
         <v>26</v>
       </c>
       <c r="L61" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
     </row>
     <row r="62" ht="30" spans="1:12">
       <c r="A62" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5131,7 +5149,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5143,24 +5161,24 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L62" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="63" ht="42" spans="1:12">
       <c r="A63" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B63" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5169,7 +5187,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5184,12 +5202,12 @@
         <v>26</v>
       </c>
       <c r="L63" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5198,7 +5216,7 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5207,7 +5225,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5219,15 +5237,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L64" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B65" t="s">
         <v>29</v>
@@ -5242,7 +5260,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5257,12 +5275,12 @@
         <v>26</v>
       </c>
       <c r="L65" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="66" ht="54" spans="1:12">
       <c r="A66" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5280,7 +5298,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5292,15 +5310,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L66" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5318,7 +5336,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5333,12 +5351,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5356,7 +5374,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5371,12 +5389,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B69" t="s">
         <v>23</v>
@@ -5394,7 +5412,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5409,12 +5427,12 @@
         <v>26</v>
       </c>
       <c r="L69" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" ht="42" spans="1:12">
       <c r="A70" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5432,7 +5450,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5444,15 +5462,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L70" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="71" ht="67.5" spans="1:12">
       <c r="A71" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5470,7 +5488,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5482,15 +5500,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L71" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" ht="42" spans="1:12">
       <c r="A72" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B72" t="s">
         <v>23</v>
@@ -5508,7 +5526,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5523,12 +5541,12 @@
         <v>26</v>
       </c>
       <c r="L72" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5546,7 +5564,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5561,12 +5579,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
     </row>
     <row r="74" ht="57" spans="1:12">
       <c r="A74" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B74" t="s">
         <v>23</v>
@@ -5584,7 +5602,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5599,12 +5617,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75" ht="42" spans="1:12">
       <c r="A75" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5622,7 +5640,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5634,15 +5652,15 @@
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L75" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
     </row>
     <row r="76" ht="54" spans="1:12">
       <c r="A76" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5660,7 +5678,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5675,12 +5693,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="77" ht="55.5" spans="1:12">
       <c r="A77" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5698,7 +5716,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5710,15 +5728,15 @@
         <v>15</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78" ht="210" spans="1:12">
       <c r="A78" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5736,7 +5754,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5751,12 +5769,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="79" ht="55.5" spans="1:12">
       <c r="A79" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5774,7 +5792,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5789,12 +5807,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="80" ht="55.5" spans="1:12">
       <c r="A80" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5812,7 +5830,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5827,12 +5845,12 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B81" t="s">
         <v>107</v>
@@ -5850,7 +5868,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5865,12 +5883,12 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5888,7 +5906,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5903,12 +5921,12 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="83" ht="28.5" spans="1:12">
       <c r="A83" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B83" t="s">
         <v>29</v>
@@ -5926,7 +5944,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5941,12 +5959,12 @@
         <v>26</v>
       </c>
       <c r="L83" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="84" ht="28.5" spans="1:12">
       <c r="A84" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5964,7 +5982,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5976,15 +5994,15 @@
         <v>15</v>
       </c>
       <c r="K84" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L84" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="85" ht="54" spans="1:12">
       <c r="A85" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B85" t="s">
         <v>107</v>
@@ -6002,7 +6020,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6017,12 +6035,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="86" ht="27" spans="1:12">
       <c r="A86" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6040,7 +6058,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6055,12 +6073,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="87" ht="40.5" spans="1:12">
       <c r="A87" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6078,7 +6096,7 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
@@ -6093,21 +6111,21 @@
         <v>15</v>
       </c>
       <c r="L87" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="88" ht="28.5" spans="1:12">
       <c r="A88" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B88" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -6116,7 +6134,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6131,12 +6149,12 @@
         <v>26</v>
       </c>
       <c r="L88" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6145,7 +6163,7 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -6169,21 +6187,21 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="90" ht="90" spans="1:12">
       <c r="A90" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B90" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -6192,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6207,12 +6225,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="91" ht="42" spans="1:12">
       <c r="A91" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6221,7 +6239,7 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
@@ -6230,7 +6248,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6242,15 +6260,15 @@
         <v>15</v>
       </c>
       <c r="K91" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L91" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="92" ht="55.5" spans="1:12">
       <c r="A92" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6268,7 +6286,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6280,24 +6298,24 @@
         <v>15</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L92" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="93" ht="150" spans="1:12">
       <c r="A93" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B93" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -6306,7 +6324,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6318,15 +6336,15 @@
         <v>15</v>
       </c>
       <c r="K93" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="L93" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="94" ht="42" spans="1:12">
       <c r="A94" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6344,7 +6362,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6356,7 +6374,7 @@
         <v>15</v>
       </c>
       <c r="K94" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L94" t="s">
         <v>21</v>
@@ -6364,7 +6382,7 @@
     </row>
     <row r="95" ht="40.5" spans="1:12">
       <c r="A95" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6382,7 +6400,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6402,7 +6420,7 @@
     </row>
     <row r="96" ht="54" spans="1:12">
       <c r="A96" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6420,7 +6438,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6435,12 +6453,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="97" ht="40.5" spans="1:12">
       <c r="A97" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B97" t="s">
         <v>23</v>
@@ -6458,7 +6476,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6478,7 +6496,7 @@
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B98" t="s">
         <v>23</v>
@@ -6496,7 +6514,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6511,12 +6529,12 @@
         <v>15</v>
       </c>
       <c r="L98" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="99" ht="54" spans="1:12">
       <c r="A99" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6534,7 +6552,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6546,10 +6564,10 @@
         <v>15</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L99" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
   </sheetData>
@@ -6570,47 +6588,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B5" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -6618,7 +6636,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
@@ -6626,7 +6644,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B8" t="s">
         <v>93</v>
@@ -6634,7 +6652,7 @@
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B9" t="s">
         <v>81</v>
@@ -6642,50 +6660,50 @@
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B10" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B11" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B12" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B13" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B14" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
@@ -6707,616 +6725,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B3" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C3" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D3" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F3" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D4" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B5" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C5" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D5" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E5" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F5" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B6" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C6" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D6" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E6" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F6" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B7" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C7" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D7" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E7" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F7" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B8" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C8" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D8" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E8" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="F8" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B9" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C9" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D9" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E9" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F9" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B10" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="C10" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D10" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E10" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F10" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B11" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C11" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D11" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E11" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F11" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B12" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C12" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D12" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E12" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="F12" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B13" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C13" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D13" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E13" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="F13" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B14" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C14" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D14" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E14" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F14" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B15" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="D15" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E15" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F15" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B16" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C16" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D16" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E16" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="F16" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B17" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C17" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D17" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E17" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F17" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B18" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C18" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D18" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E18" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="F18" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B19" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C19" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D19" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E19" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="F19" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B20" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C20" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="D20" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E20" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F20" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B21" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="C21" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D21" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="E21" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F21" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B22" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C22" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D22" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E22" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F22" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B23" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C23" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D23" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E23" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F23" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B24" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C24" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D24" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="E24" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F24" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B25" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C25" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D25" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E25" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="F25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B26" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C26" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="D26" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="E26" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="F26" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B27" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C27" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="D27" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E27" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B28" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C28" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="D28" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E28" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="F28" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B29" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C29" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="D29" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="E29" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="F29" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B30" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="C30" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D30" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="E30" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="F30" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B31" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="C31" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D31" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_gy(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_盖亚之心（上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="502">
   <si>
     <t>ID</t>
   </si>
@@ -264,6 +264,9 @@
     <t>当视线、脚步、地点与回忆在三楼的走廊处如同最精密的齿轮般彼此咬合之时，记忆的水晶球终于转到了它相对清晰的一面。其折射出的微光在日益坍塌的楼道间勾勒出数道朦胧白影，宛若被疾风卷起的陈旧相片。</t>
   </si>
   <si>
+    <t>14 enhanced_horror-free</t>
+  </si>
+  <si>
     <t>源类型=type:txt_pb; 层级=8</t>
   </si>
   <si>
@@ -630,7 +633,41 @@
     <t>64</t>
   </si>
   <si>
-    <t>源类型=type:exeBC; 层级=47</t>
+    <t>7 enhanced litesaturation-horror</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:exeBC; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=47</t>
+    </r>
   </si>
   <si>
     <t>65</t>
@@ -918,6 +955,12 @@
   </si>
   <si>
     <t>大卫看着那只飞蛾，他的下颌线绷紧了一瞬，然后他转过头来看你，语气里带着一种像他这般在生死边缘走过的人特有的、近乎莽撞的平静。</t>
+  </si>
+  <si>
+    <t>1 enhanced alex-morgan-dark-suspense-thriller</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music1)</t>
   </si>
   <si>
     <t>86</t>
@@ -3524,7 +3567,7 @@
         <v>15</v>
       </c>
       <c r="I19" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="J19" t="s">
         <v>15</v>
@@ -3533,12 +3576,12 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="54" spans="1:12">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
         <v>13</v>
@@ -3556,7 +3599,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3568,15 +3611,15 @@
         <v>15</v>
       </c>
       <c r="K20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" ht="54" spans="1:12">
       <c r="A21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B21" t="s">
         <v>13</v>
@@ -3594,7 +3637,7 @@
         <v>15</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3609,12 +3652,12 @@
         <v>15</v>
       </c>
       <c r="L21" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" ht="69" spans="1:12">
       <c r="A22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3632,7 +3675,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3647,12 +3690,12 @@
         <v>15</v>
       </c>
       <c r="L22" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" ht="40.5" spans="1:12">
       <c r="A23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" t="s">
         <v>13</v>
@@ -3670,7 +3713,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3685,12 +3728,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" ht="55.5" spans="1:12">
       <c r="A24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3708,7 +3751,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3723,12 +3766,12 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="25" ht="67.5" spans="1:12">
       <c r="A25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B25" t="s">
         <v>13</v>
@@ -3746,7 +3789,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3761,12 +3804,12 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" ht="67.5" spans="1:12">
       <c r="A26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
         <v>13</v>
@@ -3784,7 +3827,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3799,15 +3842,15 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" ht="30" spans="1:12">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C27" t="s">
         <v>14</v>
@@ -3822,7 +3865,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3837,12 +3880,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" ht="67.5" spans="1:12">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>13</v>
@@ -3860,7 +3903,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3875,15 +3918,15 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B29" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C29" t="s">
         <v>14</v>
@@ -3898,7 +3941,7 @@
         <v>15</v>
       </c>
       <c r="G29" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H29" t="s">
         <v>15</v>
@@ -3913,12 +3956,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3936,7 +3979,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3951,12 +3994,12 @@
         <v>15</v>
       </c>
       <c r="L30" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" ht="40.5" spans="1:12">
       <c r="A31" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3974,7 +4017,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3989,12 +4032,12 @@
         <v>15</v>
       </c>
       <c r="L31" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" ht="54" spans="1:12">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -4012,7 +4055,7 @@
         <v>15</v>
       </c>
       <c r="G32" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H32" t="s">
         <v>15</v>
@@ -4024,15 +4067,15 @@
         <v>15</v>
       </c>
       <c r="K32" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="L32" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" ht="27" spans="1:12">
       <c r="A33" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B33" t="s">
         <v>13</v>
@@ -4050,7 +4093,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -4065,12 +4108,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="34" ht="55.5" spans="1:12">
       <c r="A34" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -4088,7 +4131,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -4103,12 +4146,12 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="35" ht="42" spans="1:12">
       <c r="A35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B35" t="s">
         <v>13</v>
@@ -4126,7 +4169,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -4141,12 +4184,12 @@
         <v>15</v>
       </c>
       <c r="L35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="36" ht="67.5" spans="1:12">
       <c r="A36" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -4164,7 +4207,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -4176,15 +4219,15 @@
         <v>15</v>
       </c>
       <c r="K36" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L36" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="37" ht="42" spans="1:12">
       <c r="A37" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -4202,7 +4245,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -4217,12 +4260,12 @@
         <v>15</v>
       </c>
       <c r="L37" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="38" ht="58.5" spans="1:12">
       <c r="A38" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -4240,7 +4283,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4255,12 +4298,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="39" ht="28.5" spans="1:12">
       <c r="A39" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4278,7 +4321,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4293,12 +4336,12 @@
         <v>15</v>
       </c>
       <c r="L39" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" ht="27" spans="1:12">
       <c r="A40" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4316,7 +4359,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4331,12 +4374,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="41" ht="54" spans="1:12">
       <c r="A41" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4354,7 +4397,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4369,12 +4412,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="42" ht="54" spans="1:12">
       <c r="A42" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4392,7 +4435,7 @@
         <v>15</v>
       </c>
       <c r="G42" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H42" t="s">
         <v>15</v>
@@ -4404,15 +4447,15 @@
         <v>15</v>
       </c>
       <c r="K42" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L42" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="43" spans="1:12">
       <c r="A43" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4445,12 +4488,12 @@
         <v>15</v>
       </c>
       <c r="L43" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" ht="30" spans="1:12">
       <c r="A44" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B44" t="s">
         <v>23</v>
@@ -4468,7 +4511,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4483,12 +4526,12 @@
         <v>26</v>
       </c>
       <c r="L44" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="45" ht="30" spans="1:12">
       <c r="A45" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B45" t="s">
         <v>13</v>
@@ -4506,7 +4549,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4518,15 +4561,15 @@
         <v>15</v>
       </c>
       <c r="K45" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L45" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" ht="40.5" spans="1:12">
       <c r="A46" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4544,7 +4587,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4559,15 +4602,15 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="47" spans="1:12">
       <c r="A47" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B47" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
@@ -4582,7 +4625,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4597,12 +4640,12 @@
         <v>15</v>
       </c>
       <c r="L47" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="48" ht="30" spans="1:12">
       <c r="A48" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B48" t="s">
         <v>23</v>
@@ -4620,7 +4663,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4635,12 +4678,12 @@
         <v>26</v>
       </c>
       <c r="L48" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="49" ht="30" spans="1:12">
       <c r="A49" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4658,7 +4701,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4673,12 +4716,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:12">
       <c r="A50" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B50" t="s">
         <v>23</v>
@@ -4696,7 +4739,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4711,12 +4754,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4734,7 +4777,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4749,12 +4792,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" ht="30" spans="1:12">
       <c r="A52" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B52" t="s">
         <v>23</v>
@@ -4772,7 +4815,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4787,12 +4830,12 @@
         <v>15</v>
       </c>
       <c r="L52" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="53" ht="42" spans="1:12">
       <c r="A53" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B53" t="s">
         <v>13</v>
@@ -4810,7 +4853,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4822,15 +4865,15 @@
         <v>15</v>
       </c>
       <c r="K53" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L53" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="54" ht="55.5" spans="1:12">
       <c r="A54" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4848,7 +4891,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4863,12 +4906,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="55" ht="27" spans="1:12">
       <c r="A55" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4886,7 +4929,7 @@
         <v>15</v>
       </c>
       <c r="G55" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H55" t="s">
         <v>15</v>
@@ -4901,12 +4944,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="56" ht="40.5" spans="1:12">
       <c r="A56" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4924,7 +4967,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4939,12 +4982,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="57" ht="55.5" spans="1:12">
       <c r="A57" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4962,7 +5005,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4974,12 +5017,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="58" ht="45" spans="1:12">
       <c r="A58" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -5003,7 +5046,7 @@
         <v>15</v>
       </c>
       <c r="I58" t="s">
-        <v>15</v>
+        <v>199</v>
       </c>
       <c r="J58" t="s">
         <v>15</v>
@@ -5011,13 +5054,13 @@
       <c r="K58" t="s">
         <v>15</v>
       </c>
-      <c r="L58" t="s">
-        <v>198</v>
+      <c r="L58" s="2" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="59" ht="90" spans="1:12">
       <c r="A59" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -5035,7 +5078,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -5047,15 +5090,15 @@
         <v>15</v>
       </c>
       <c r="K59" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="L59" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="60" ht="90" spans="1:12">
       <c r="A60" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -5073,7 +5116,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -5088,12 +5131,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="61" ht="30" spans="1:12">
       <c r="A61" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B61" t="s">
         <v>23</v>
@@ -5111,7 +5154,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -5126,12 +5169,12 @@
         <v>26</v>
       </c>
       <c r="L61" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="62" ht="30" spans="1:12">
       <c r="A62" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -5149,7 +5192,7 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
@@ -5161,24 +5204,24 @@
         <v>15</v>
       </c>
       <c r="K62" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L62" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="63" ht="42" spans="1:12">
       <c r="A63" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B63" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C63" t="s">
         <v>14</v>
       </c>
       <c r="D63" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E63" t="s">
         <v>15</v>
@@ -5187,7 +5230,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -5202,12 +5245,12 @@
         <v>26</v>
       </c>
       <c r="L63" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
     </row>
     <row r="64" ht="54" spans="1:12">
       <c r="A64" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B64" t="s">
         <v>13</v>
@@ -5216,7 +5259,7 @@
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -5225,7 +5268,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -5237,15 +5280,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L64" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
     </row>
     <row r="65" spans="1:12">
       <c r="A65" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B65" t="s">
         <v>29</v>
@@ -5260,7 +5303,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5275,12 +5318,12 @@
         <v>26</v>
       </c>
       <c r="L65" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
     </row>
     <row r="66" ht="54" spans="1:12">
       <c r="A66" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B66" t="s">
         <v>13</v>
@@ -5298,7 +5341,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5310,15 +5353,15 @@
         <v>15</v>
       </c>
       <c r="K66" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L66" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5336,7 +5379,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5351,12 +5394,12 @@
         <v>15</v>
       </c>
       <c r="L67" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
     </row>
     <row r="68" ht="40.5" spans="1:12">
       <c r="A68" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B68" t="s">
         <v>13</v>
@@ -5374,7 +5417,7 @@
         <v>15</v>
       </c>
       <c r="G68" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="H68" t="s">
         <v>15</v>
@@ -5389,12 +5432,12 @@
         <v>15</v>
       </c>
       <c r="L68" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="69" ht="30" spans="1:12">
       <c r="A69" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B69" t="s">
         <v>23</v>
@@ -5412,7 +5455,7 @@
         <v>15</v>
       </c>
       <c r="G69" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="H69" t="s">
         <v>15</v>
@@ -5427,12 +5470,12 @@
         <v>26</v>
       </c>
       <c r="L69" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
     </row>
     <row r="70" ht="42" spans="1:12">
       <c r="A70" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B70" t="s">
         <v>13</v>
@@ -5450,7 +5493,7 @@
         <v>15</v>
       </c>
       <c r="G70" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H70" t="s">
         <v>15</v>
@@ -5462,15 +5505,15 @@
         <v>15</v>
       </c>
       <c r="K70" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L70" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="71" ht="67.5" spans="1:12">
       <c r="A71" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B71" t="s">
         <v>13</v>
@@ -5488,7 +5531,7 @@
         <v>15</v>
       </c>
       <c r="G71" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="H71" t="s">
         <v>15</v>
@@ -5500,15 +5543,15 @@
         <v>15</v>
       </c>
       <c r="K71" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L71" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
     </row>
     <row r="72" ht="42" spans="1:12">
       <c r="A72" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B72" t="s">
         <v>23</v>
@@ -5526,7 +5569,7 @@
         <v>15</v>
       </c>
       <c r="G72" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="H72" t="s">
         <v>15</v>
@@ -5541,12 +5584,12 @@
         <v>26</v>
       </c>
       <c r="L72" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="73" ht="40.5" spans="1:12">
       <c r="A73" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B73" t="s">
         <v>13</v>
@@ -5564,7 +5607,7 @@
         <v>15</v>
       </c>
       <c r="G73" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="H73" t="s">
         <v>15</v>
@@ -5579,12 +5622,12 @@
         <v>15</v>
       </c>
       <c r="L73" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" ht="57" spans="1:12">
       <c r="A74" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B74" t="s">
         <v>23</v>
@@ -5602,7 +5645,7 @@
         <v>15</v>
       </c>
       <c r="G74" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="H74" t="s">
         <v>15</v>
@@ -5617,12 +5660,12 @@
         <v>15</v>
       </c>
       <c r="L74" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
     </row>
     <row r="75" ht="42" spans="1:12">
       <c r="A75" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B75" t="s">
         <v>13</v>
@@ -5640,7 +5683,7 @@
         <v>15</v>
       </c>
       <c r="G75" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="H75" t="s">
         <v>15</v>
@@ -5652,15 +5695,15 @@
         <v>15</v>
       </c>
       <c r="K75" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L75" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
     </row>
     <row r="76" ht="54" spans="1:12">
       <c r="A76" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B76" t="s">
         <v>13</v>
@@ -5678,7 +5721,7 @@
         <v>15</v>
       </c>
       <c r="G76" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H76" t="s">
         <v>15</v>
@@ -5693,12 +5736,12 @@
         <v>15</v>
       </c>
       <c r="L76" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" ht="55.5" spans="1:12">
       <c r="A77" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B77" t="s">
         <v>13</v>
@@ -5716,7 +5759,7 @@
         <v>15</v>
       </c>
       <c r="G77" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="H77" t="s">
         <v>15</v>
@@ -5728,15 +5771,15 @@
         <v>15</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="L77" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="78" ht="210" spans="1:12">
       <c r="A78" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B78" t="s">
         <v>13</v>
@@ -5754,7 +5797,7 @@
         <v>15</v>
       </c>
       <c r="G78" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="H78" t="s">
         <v>15</v>
@@ -5769,12 +5812,12 @@
         <v>15</v>
       </c>
       <c r="L78" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
     </row>
     <row r="79" ht="55.5" spans="1:12">
       <c r="A79" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B79" t="s">
         <v>13</v>
@@ -5792,7 +5835,7 @@
         <v>15</v>
       </c>
       <c r="G79" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H79" t="s">
         <v>15</v>
@@ -5807,12 +5850,12 @@
         <v>15</v>
       </c>
       <c r="L79" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="80" ht="55.5" spans="1:12">
       <c r="A80" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B80" t="s">
         <v>13</v>
@@ -5830,7 +5873,7 @@
         <v>15</v>
       </c>
       <c r="G80" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="H80" t="s">
         <v>15</v>
@@ -5845,15 +5888,15 @@
         <v>15</v>
       </c>
       <c r="L80" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B81" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C81" t="s">
         <v>14</v>
@@ -5868,7 +5911,7 @@
         <v>15</v>
       </c>
       <c r="G81" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="H81" t="s">
         <v>15</v>
@@ -5883,12 +5926,12 @@
         <v>15</v>
       </c>
       <c r="L81" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="82" spans="1:12">
       <c r="A82" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B82" t="s">
         <v>13</v>
@@ -5906,7 +5949,7 @@
         <v>15</v>
       </c>
       <c r="G82" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="H82" t="s">
         <v>15</v>
@@ -5921,12 +5964,12 @@
         <v>15</v>
       </c>
       <c r="L82" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="83" ht="28.5" spans="1:12">
       <c r="A83" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B83" t="s">
         <v>29</v>
@@ -5944,7 +5987,7 @@
         <v>15</v>
       </c>
       <c r="G83" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H83" t="s">
         <v>15</v>
@@ -5959,12 +6002,12 @@
         <v>26</v>
       </c>
       <c r="L83" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="84" ht="28.5" spans="1:12">
       <c r="A84" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B84" t="s">
         <v>13</v>
@@ -5982,7 +6025,7 @@
         <v>15</v>
       </c>
       <c r="G84" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="H84" t="s">
         <v>15</v>
@@ -5994,18 +6037,18 @@
         <v>15</v>
       </c>
       <c r="K84" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L84" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="85" ht="54" spans="1:12">
       <c r="A85" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B85" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C85" t="s">
         <v>14</v>
@@ -6020,7 +6063,7 @@
         <v>15</v>
       </c>
       <c r="G85" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H85" t="s">
         <v>15</v>
@@ -6035,12 +6078,12 @@
         <v>15</v>
       </c>
       <c r="L85" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="86" ht="27" spans="1:12">
       <c r="A86" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B86" t="s">
         <v>13</v>
@@ -6058,7 +6101,7 @@
         <v>15</v>
       </c>
       <c r="G86" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H86" t="s">
         <v>15</v>
@@ -6073,12 +6116,12 @@
         <v>15</v>
       </c>
       <c r="L86" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="87" ht="40.5" spans="1:12">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="87" ht="45" spans="1:12">
       <c r="A87" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B87" t="s">
         <v>13</v>
@@ -6096,36 +6139,36 @@
         <v>15</v>
       </c>
       <c r="G87" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="H87" t="s">
         <v>15</v>
       </c>
       <c r="I87" t="s">
-        <v>15</v>
+        <v>289</v>
       </c>
       <c r="J87" t="s">
         <v>15</v>
       </c>
       <c r="K87" t="s">
-        <v>15</v>
+        <v>290</v>
       </c>
       <c r="L87" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="88" ht="28.5" spans="1:12">
       <c r="A88" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B88" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C88" t="s">
         <v>14</v>
       </c>
       <c r="D88" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E88" t="s">
         <v>15</v>
@@ -6134,7 +6177,7 @@
         <v>15</v>
       </c>
       <c r="G88" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H88" t="s">
         <v>15</v>
@@ -6149,12 +6192,12 @@
         <v>26</v>
       </c>
       <c r="L88" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="89" spans="1:12">
       <c r="A89" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="B89" t="s">
         <v>13</v>
@@ -6163,7 +6206,7 @@
         <v>14</v>
       </c>
       <c r="D89" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E89" t="s">
         <v>15</v>
@@ -6187,21 +6230,21 @@
         <v>15</v>
       </c>
       <c r="L89" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="90" ht="90" spans="1:12">
       <c r="A90" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B90" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C90" t="s">
         <v>14</v>
       </c>
       <c r="D90" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E90" t="s">
         <v>15</v>
@@ -6210,7 +6253,7 @@
         <v>15</v>
       </c>
       <c r="G90" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H90" t="s">
         <v>15</v>
@@ -6225,12 +6268,12 @@
         <v>15</v>
       </c>
       <c r="L90" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="91" ht="42" spans="1:12">
       <c r="A91" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B91" t="s">
         <v>13</v>
@@ -6239,7 +6282,7 @@
         <v>14</v>
       </c>
       <c r="D91" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E91" t="s">
         <v>15</v>
@@ -6248,7 +6291,7 @@
         <v>15</v>
       </c>
       <c r="G91" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="H91" t="s">
         <v>15</v>
@@ -6260,15 +6303,15 @@
         <v>15</v>
       </c>
       <c r="K91" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L91" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="92" ht="55.5" spans="1:12">
       <c r="A92" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B92" t="s">
         <v>13</v>
@@ -6286,7 +6329,7 @@
         <v>15</v>
       </c>
       <c r="G92" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H92" t="s">
         <v>15</v>
@@ -6298,24 +6341,24 @@
         <v>15</v>
       </c>
       <c r="K92" s="3" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="L92" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="93" ht="150" spans="1:12">
       <c r="A93" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B93" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C93" t="s">
         <v>14</v>
       </c>
       <c r="D93" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E93" t="s">
         <v>15</v>
@@ -6324,7 +6367,7 @@
         <v>15</v>
       </c>
       <c r="G93" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="H93" t="s">
         <v>15</v>
@@ -6336,15 +6379,15 @@
         <v>15</v>
       </c>
       <c r="K93" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="L93" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="94" ht="42" spans="1:12">
       <c r="A94" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B94" t="s">
         <v>13</v>
@@ -6362,7 +6405,7 @@
         <v>15</v>
       </c>
       <c r="G94" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="H94" t="s">
         <v>15</v>
@@ -6374,7 +6417,7 @@
         <v>15</v>
       </c>
       <c r="K94" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L94" t="s">
         <v>21</v>
@@ -6382,7 +6425,7 @@
     </row>
     <row r="95" ht="40.5" spans="1:12">
       <c r="A95" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B95" t="s">
         <v>13</v>
@@ -6400,7 +6443,7 @@
         <v>15</v>
       </c>
       <c r="G95" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H95" t="s">
         <v>15</v>
@@ -6420,7 +6463,7 @@
     </row>
     <row r="96" ht="54" spans="1:12">
       <c r="A96" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B96" t="s">
         <v>13</v>
@@ -6438,7 +6481,7 @@
         <v>15</v>
       </c>
       <c r="G96" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H96" t="s">
         <v>15</v>
@@ -6453,12 +6496,12 @@
         <v>15</v>
       </c>
       <c r="L96" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="97" ht="40.5" spans="1:12">
       <c r="A97" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B97" t="s">
         <v>23</v>
@@ -6476,7 +6519,7 @@
         <v>15</v>
       </c>
       <c r="G97" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="H97" t="s">
         <v>15</v>
@@ -6496,7 +6539,7 @@
     </row>
     <row r="98" ht="40.5" spans="1:12">
       <c r="A98" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B98" t="s">
         <v>23</v>
@@ -6514,7 +6557,7 @@
         <v>15</v>
       </c>
       <c r="G98" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="H98" t="s">
         <v>15</v>
@@ -6529,12 +6572,12 @@
         <v>15</v>
       </c>
       <c r="L98" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="99" ht="54" spans="1:12">
       <c r="A99" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B99" t="s">
         <v>13</v>
@@ -6552,7 +6595,7 @@
         <v>15</v>
       </c>
       <c r="G99" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H99" t="s">
         <v>15</v>
@@ -6564,10 +6607,10 @@
         <v>15</v>
       </c>
       <c r="K99" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="L99" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
   </sheetData>
@@ -6588,47 +6631,47 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="2" ht="30" spans="1:2">
       <c r="A2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B4" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
@@ -6636,7 +6679,7 @@
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B7" t="s">
         <v>49</v>
@@ -6644,66 +6687,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B10" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B11" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B12" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B13" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B14" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B15" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
   </sheetData>
@@ -6725,616 +6768,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="C2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="E2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="F2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="D3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E3" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F3" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="C4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="D4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="E4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B5" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C5" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D5" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="E5" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F5" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B6" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="C6" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="D6" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="E6" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="F6" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B7" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="C7" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="D7" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E7" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="F7" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B8" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="C8" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="D8" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E8" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="F8" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="B9" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C9" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="D9" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E9" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F9" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B10" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="C10" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="D10" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E10" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F10" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B11" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="C11" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="D11" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="E11" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F11" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B12" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="C12" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D12" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E12" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="F12" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B13" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C13" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D13" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E13" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F13" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B14" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="C14" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="D14" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="E14" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="F14" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B15" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C15" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D15" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="E15" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F15" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B16" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="C16" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="D16" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="E16" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="F16" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B17" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C17" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D17" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="E17" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="F17" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B18" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="C18" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D18" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E18" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F18" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B19" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C19" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D19" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E19" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F19" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B20" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="C20" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="D20" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E20" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F20" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B21" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C21" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D21" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E21" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="F21" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B22" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="C22" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="D22" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E22" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="F22" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B23" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C23" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D23" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E23" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="F23" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B24" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="C24" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D24" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="E24" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F24" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B25" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C25" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D25" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="E25" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F25" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B26" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="C26" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D26" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="E26" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="F26" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B27" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C27" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D27" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="E27" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="F27" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B28" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="C28" t="s">
+        <v>485</v>
+      </c>
+      <c r="D28" t="s">
         <v>481</v>
       </c>
-      <c r="D28" t="s">
-        <v>477</v>
-      </c>
       <c r="E28" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="F28" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B29" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="C29" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D29" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="E29" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="F29" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B30" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C30" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D30" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E30" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="F30" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B31" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C31" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D31" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
     </row>
   </sheetData>
